--- a/output/yearly_total_coral_cover_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_78_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.282011739871779</v>
+        <v>1.277849129605772</v>
       </c>
       <c r="C3" t="n">
-        <v>4.63124447844574</v>
+        <v>4.641317209891312</v>
       </c>
       <c r="D3" t="n">
-        <v>6.051065882660632</v>
+        <v>6.116195025360366</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96432210097815</v>
+        <v>12.03536136485745</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.457526079973223</v>
+        <v>1.441501590175495</v>
       </c>
       <c r="C4" t="n">
-        <v>5.138311258304087</v>
+        <v>5.202826831584141</v>
       </c>
       <c r="D4" t="n">
-        <v>6.240111862851474</v>
+        <v>6.442851147756487</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83594920112878</v>
+        <v>13.08717956951612</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.694260098442327</v>
+        <v>1.657579317433653</v>
       </c>
       <c r="C5" t="n">
-        <v>5.763946774706201</v>
+        <v>5.958990586286007</v>
       </c>
       <c r="D5" t="n">
-        <v>6.608441766006275</v>
+        <v>6.841917855846185</v>
       </c>
       <c r="E5" t="n">
-        <v>14.0666486391548</v>
+        <v>14.45848775956584</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.953649001471145</v>
+        <v>1.890055863720654</v>
       </c>
       <c r="C6" t="n">
-        <v>6.548667799575319</v>
+        <v>6.87913151085839</v>
       </c>
       <c r="D6" t="n">
-        <v>6.954212448014322</v>
+        <v>7.29348839364985</v>
       </c>
       <c r="E6" t="n">
-        <v>15.45652924906079</v>
+        <v>16.0626757682289</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.238900520076821</v>
+        <v>2.132283644079021</v>
       </c>
       <c r="C7" t="n">
-        <v>7.449348333979381</v>
+        <v>7.956415541885045</v>
       </c>
       <c r="D7" t="n">
-        <v>7.297643320968848</v>
+        <v>7.734900966698788</v>
       </c>
       <c r="E7" t="n">
-        <v>16.98589217502505</v>
+        <v>17.82360015266286</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.423184015344463</v>
+        <v>1.31476831668513</v>
       </c>
       <c r="C8" t="n">
-        <v>5.105502858623791</v>
+        <v>5.628915598572149</v>
       </c>
       <c r="D8" t="n">
-        <v>5.493851154153551</v>
+        <v>6.016487413763632</v>
       </c>
       <c r="E8" t="n">
-        <v>12.0225380281218</v>
+        <v>12.96017132902091</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.800078189173338</v>
+        <v>1.641436941805873</v>
       </c>
       <c r="C9" t="n">
-        <v>6.263428952909951</v>
+        <v>6.937001910341384</v>
       </c>
       <c r="D9" t="n">
-        <v>5.936904180214872</v>
+        <v>6.552376065344093</v>
       </c>
       <c r="E9" t="n">
-        <v>14.00041132229816</v>
+        <v>15.13081491749135</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.197658723901237</v>
+        <v>1.981749395833596</v>
       </c>
       <c r="C10" t="n">
-        <v>7.576168080310635</v>
+        <v>8.380996354999372</v>
       </c>
       <c r="D10" t="n">
-        <v>6.455446141656718</v>
+        <v>7.179084514387548</v>
       </c>
       <c r="E10" t="n">
-        <v>16.22927294586859</v>
+        <v>17.54183026522051</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.603427299690287</v>
+        <v>2.311458348750708</v>
       </c>
       <c r="C11" t="n">
-        <v>9.009088724790665</v>
+        <v>9.936118507250628</v>
       </c>
       <c r="D11" t="n">
-        <v>6.89872076792572</v>
+        <v>7.870349469645167</v>
       </c>
       <c r="E11" t="n">
-        <v>18.51123679240667</v>
+        <v>20.1179263256465</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.015565018697481</v>
+        <v>2.622012420400984</v>
       </c>
       <c r="C12" t="n">
-        <v>10.48564574796481</v>
+        <v>11.5706872218974</v>
       </c>
       <c r="D12" t="n">
-        <v>7.40304451109942</v>
+        <v>8.505718441025238</v>
       </c>
       <c r="E12" t="n">
-        <v>20.90425527776171</v>
+        <v>22.69841808332362</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.416580105216084</v>
+        <v>2.902673715399591</v>
       </c>
       <c r="C13" t="n">
-        <v>12.04903143114275</v>
+        <v>13.22242230725572</v>
       </c>
       <c r="D13" t="n">
-        <v>7.792001346619569</v>
+        <v>9.043809743030533</v>
       </c>
       <c r="E13" t="n">
-        <v>23.25761288297841</v>
+        <v>25.16890576568585</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.976425025758551</v>
+        <v>1.6622952128307</v>
       </c>
       <c r="C14" t="n">
-        <v>8.470391565039929</v>
+        <v>9.268199019419056</v>
       </c>
       <c r="D14" t="n">
-        <v>5.930247007502857</v>
+        <v>6.851911752249765</v>
       </c>
       <c r="E14" t="n">
-        <v>16.37706359830134</v>
+        <v>17.78240598449952</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.034976458839831</v>
+        <v>1.678700216968664</v>
       </c>
       <c r="C15" t="n">
-        <v>9.16021658942895</v>
+        <v>10.02013922105577</v>
       </c>
       <c r="D15" t="n">
-        <v>5.922736637565371</v>
+        <v>6.93690165100641</v>
       </c>
       <c r="E15" t="n">
-        <v>17.11792968583415</v>
+        <v>18.63574108903085</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.384743713431842</v>
+        <v>1.926719139492535</v>
       </c>
       <c r="C16" t="n">
-        <v>10.83408660769272</v>
+        <v>11.80317958403179</v>
       </c>
       <c r="D16" t="n">
-        <v>6.387741437681872</v>
+        <v>7.518007934627139</v>
       </c>
       <c r="E16" t="n">
-        <v>19.60657175880643</v>
+        <v>21.24790665815146</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.923911341058389</v>
+        <v>1.531919117706723</v>
       </c>
       <c r="C17" t="n">
-        <v>9.993465135931388</v>
+        <v>10.81875170855238</v>
       </c>
       <c r="D17" t="n">
-        <v>5.90746064328729</v>
+        <v>7.021528303112485</v>
       </c>
       <c r="E17" t="n">
-        <v>17.82483712027707</v>
+        <v>19.37219912937159</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.208932334555323</v>
+        <v>1.733098857260979</v>
       </c>
       <c r="C18" t="n">
-        <v>11.67704463899016</v>
+        <v>12.58870537463079</v>
       </c>
       <c r="D18" t="n">
-        <v>6.311086576934281</v>
+        <v>7.567890535479921</v>
       </c>
       <c r="E18" t="n">
-        <v>20.19706355047976</v>
+        <v>21.88969476737169</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.231453626890745</v>
+        <v>1.722142552881585</v>
       </c>
       <c r="C19" t="n">
-        <v>12.50866348430355</v>
+        <v>13.40398793814551</v>
       </c>
       <c r="D19" t="n">
-        <v>6.402457835768532</v>
+        <v>7.724351667105734</v>
       </c>
       <c r="E19" t="n">
-        <v>21.14257494696282</v>
+        <v>22.85048215813283</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.499961624002248</v>
+        <v>1.902793947940041</v>
       </c>
       <c r="C20" t="n">
-        <v>14.40122762116533</v>
+        <v>15.32741822282882</v>
       </c>
       <c r="D20" t="n">
-        <v>6.789737670139814</v>
+        <v>8.219663018852335</v>
       </c>
       <c r="E20" t="n">
-        <v>23.6909269153074</v>
+        <v>25.4498751896212</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.49598715173129</v>
+        <v>1.1258584497532</v>
       </c>
       <c r="C21" t="n">
-        <v>10.62971618809966</v>
+        <v>11.22649116508017</v>
       </c>
       <c r="D21" t="n">
-        <v>5.651489564359019</v>
+        <v>6.905348279791918</v>
       </c>
       <c r="E21" t="n">
-        <v>17.77719290418997</v>
+        <v>19.25769789462529</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_78_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.277849129605772</v>
+        <v>1.298210576991851</v>
       </c>
       <c r="C3" t="n">
-        <v>4.641317209891312</v>
+        <v>4.607839613176496</v>
       </c>
       <c r="D3" t="n">
-        <v>6.116195025360366</v>
+        <v>6.053068647977295</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03536136485745</v>
+        <v>11.95911883814564</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.441501590175495</v>
+        <v>1.487882612918202</v>
       </c>
       <c r="C4" t="n">
-        <v>5.202826831584141</v>
+        <v>5.04622800363047</v>
       </c>
       <c r="D4" t="n">
-        <v>6.442851147756487</v>
+        <v>6.285910498422783</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08717956951612</v>
+        <v>12.82002111497146</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.657579317433653</v>
+        <v>1.733151185427593</v>
       </c>
       <c r="C5" t="n">
-        <v>5.958990586286007</v>
+        <v>5.584653209395269</v>
       </c>
       <c r="D5" t="n">
-        <v>6.841917855846185</v>
+        <v>6.556802691588167</v>
       </c>
       <c r="E5" t="n">
-        <v>14.45848775956584</v>
+        <v>13.87460708641103</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.890055863720654</v>
+        <v>2.004987570989977</v>
       </c>
       <c r="C6" t="n">
-        <v>6.87913151085839</v>
+        <v>6.208268900707531</v>
       </c>
       <c r="D6" t="n">
-        <v>7.29348839364985</v>
+        <v>6.915664554274905</v>
       </c>
       <c r="E6" t="n">
-        <v>16.0626757682289</v>
+        <v>15.12892102597241</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.132283644079021</v>
+        <v>2.330766368823911</v>
       </c>
       <c r="C7" t="n">
-        <v>7.956415541885045</v>
+        <v>6.907317879411339</v>
       </c>
       <c r="D7" t="n">
-        <v>7.734900966698788</v>
+        <v>7.263332904137499</v>
       </c>
       <c r="E7" t="n">
-        <v>17.82360015266286</v>
+        <v>16.50141715237275</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.31476831668513</v>
+        <v>1.532532446441489</v>
       </c>
       <c r="C8" t="n">
-        <v>5.628915598572149</v>
+        <v>4.458622521947892</v>
       </c>
       <c r="D8" t="n">
-        <v>6.016487413763632</v>
+        <v>5.542580412287738</v>
       </c>
       <c r="E8" t="n">
-        <v>12.96017132902091</v>
+        <v>11.53373538067712</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.641436941805873</v>
+        <v>1.988681014167726</v>
       </c>
       <c r="C9" t="n">
-        <v>6.937001910341384</v>
+        <v>5.274567557491197</v>
       </c>
       <c r="D9" t="n">
-        <v>6.552376065344093</v>
+        <v>5.994139998653631</v>
       </c>
       <c r="E9" t="n">
-        <v>15.13081491749135</v>
+        <v>13.25738857031256</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.981749395833596</v>
+        <v>2.491680807987767</v>
       </c>
       <c r="C10" t="n">
-        <v>8.380996354999372</v>
+        <v>6.231309901632598</v>
       </c>
       <c r="D10" t="n">
-        <v>7.179084514387548</v>
+        <v>6.547231486846128</v>
       </c>
       <c r="E10" t="n">
-        <v>17.54183026522051</v>
+        <v>15.27022219646649</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.311458348750708</v>
+        <v>3.022224760423847</v>
       </c>
       <c r="C11" t="n">
-        <v>9.936118507250628</v>
+        <v>7.270699966978178</v>
       </c>
       <c r="D11" t="n">
-        <v>7.870349469645167</v>
+        <v>7.059305434685612</v>
       </c>
       <c r="E11" t="n">
-        <v>20.1179263256465</v>
+        <v>17.35223016208764</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.622012420400984</v>
+        <v>3.572090512977819</v>
       </c>
       <c r="C12" t="n">
-        <v>11.5706872218974</v>
+        <v>8.403893006093025</v>
       </c>
       <c r="D12" t="n">
-        <v>8.505718441025238</v>
+        <v>7.594404496077854</v>
       </c>
       <c r="E12" t="n">
-        <v>22.69841808332362</v>
+        <v>19.5703880151487</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.902673715399591</v>
+        <v>4.126070662719674</v>
       </c>
       <c r="C13" t="n">
-        <v>13.22242230725572</v>
+        <v>9.568942623897643</v>
       </c>
       <c r="D13" t="n">
-        <v>9.043809743030533</v>
+        <v>8.150166537483443</v>
       </c>
       <c r="E13" t="n">
-        <v>25.16890576568585</v>
+        <v>21.84517982410076</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.6622952128307</v>
+        <v>2.371676651488317</v>
       </c>
       <c r="C14" t="n">
-        <v>9.268199019419056</v>
+        <v>6.843498174424368</v>
       </c>
       <c r="D14" t="n">
-        <v>6.851911752249765</v>
+        <v>6.231584647844373</v>
       </c>
       <c r="E14" t="n">
-        <v>17.78240598449952</v>
+        <v>15.44675947375706</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.678700216968664</v>
+        <v>2.507530898801991</v>
       </c>
       <c r="C15" t="n">
-        <v>10.02013922105577</v>
+        <v>7.208472700955163</v>
       </c>
       <c r="D15" t="n">
-        <v>6.93690165100641</v>
+        <v>6.284137602452706</v>
       </c>
       <c r="E15" t="n">
-        <v>18.63574108903085</v>
+        <v>16.00014120220986</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.926719139492535</v>
+        <v>2.996568882718455</v>
       </c>
       <c r="C16" t="n">
-        <v>11.80317958403179</v>
+        <v>8.402376084089708</v>
       </c>
       <c r="D16" t="n">
-        <v>7.518007934627139</v>
+        <v>6.79279090550002</v>
       </c>
       <c r="E16" t="n">
-        <v>21.24790665815146</v>
+        <v>18.19173587230818</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.531919117706723</v>
+        <v>2.456588010428624</v>
       </c>
       <c r="C17" t="n">
-        <v>10.81875170855238</v>
+        <v>7.702262343760181</v>
       </c>
       <c r="D17" t="n">
-        <v>7.021528303112485</v>
+        <v>6.341923272324673</v>
       </c>
       <c r="E17" t="n">
-        <v>19.37219912937159</v>
+        <v>16.50077362651348</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.733098857260979</v>
+        <v>2.875175779088336</v>
       </c>
       <c r="C18" t="n">
-        <v>12.58870537463079</v>
+        <v>8.90114318775526</v>
       </c>
       <c r="D18" t="n">
-        <v>7.567890535479921</v>
+        <v>6.80750730358668</v>
       </c>
       <c r="E18" t="n">
-        <v>21.88969476737169</v>
+        <v>18.58382627043028</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.722142552881585</v>
+        <v>2.95800583289564</v>
       </c>
       <c r="C19" t="n">
-        <v>13.40398793814551</v>
+        <v>9.476761501709248</v>
       </c>
       <c r="D19" t="n">
-        <v>7.724351667105734</v>
+        <v>6.968926261118942</v>
       </c>
       <c r="E19" t="n">
-        <v>22.85048215813283</v>
+        <v>19.40369359572383</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.902793947940041</v>
+        <v>3.374934447935176</v>
       </c>
       <c r="C20" t="n">
-        <v>15.32741822282882</v>
+        <v>10.8741910014112</v>
       </c>
       <c r="D20" t="n">
-        <v>8.219663018852335</v>
+        <v>7.436787947054801</v>
       </c>
       <c r="E20" t="n">
-        <v>25.4498751896212</v>
+        <v>21.68591339640118</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.1258584497532</v>
+        <v>2.04845585481914</v>
       </c>
       <c r="C21" t="n">
-        <v>11.22649116508017</v>
+        <v>8.036655429303687</v>
       </c>
       <c r="D21" t="n">
-        <v>6.905348279791918</v>
+        <v>6.226067225746507</v>
       </c>
       <c r="E21" t="n">
-        <v>19.25769789462529</v>
+        <v>16.31117850986934</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_78_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.298210576991851</v>
+        <v>2.58075898194529</v>
       </c>
       <c r="C3" t="n">
-        <v>4.607839613176496</v>
+        <v>7.766161471186111</v>
       </c>
       <c r="D3" t="n">
-        <v>6.053068647977295</v>
+        <v>8.189364089756701</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95911883814564</v>
+        <v>18.5362845428881</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.487882612918202</v>
+        <v>1.067734933758881</v>
       </c>
       <c r="C4" t="n">
-        <v>5.04622800363047</v>
+        <v>4.618159670916909</v>
       </c>
       <c r="D4" t="n">
-        <v>6.285910498422783</v>
+        <v>5.851412396724978</v>
       </c>
       <c r="E4" t="n">
-        <v>12.82002111497146</v>
+        <v>11.53730700140077</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.733151185427593</v>
+        <v>1.167708639406054</v>
       </c>
       <c r="C5" t="n">
-        <v>5.584653209395269</v>
+        <v>5.377679511060489</v>
       </c>
       <c r="D5" t="n">
-        <v>6.556802691588167</v>
+        <v>6.154770773205898</v>
       </c>
       <c r="E5" t="n">
-        <v>13.87460708641103</v>
+        <v>12.70015892367244</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.004987570989977</v>
+        <v>1.273727421125696</v>
       </c>
       <c r="C6" t="n">
-        <v>6.208268900707531</v>
+        <v>6.325639259202347</v>
       </c>
       <c r="D6" t="n">
-        <v>6.915664554274905</v>
+        <v>6.509270038437551</v>
       </c>
       <c r="E6" t="n">
-        <v>15.12892102597241</v>
+        <v>14.10863671876559</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.330766368823911</v>
+        <v>1.379521898745226</v>
       </c>
       <c r="C7" t="n">
-        <v>6.907317879411339</v>
+        <v>7.436780538805496</v>
       </c>
       <c r="D7" t="n">
-        <v>7.263332904137499</v>
+        <v>6.870174733025604</v>
       </c>
       <c r="E7" t="n">
-        <v>16.50141715237275</v>
+        <v>15.68647717057633</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.532532446441489</v>
+        <v>1.486251310767308</v>
       </c>
       <c r="C8" t="n">
-        <v>4.458622521947892</v>
+        <v>8.762866787483583</v>
       </c>
       <c r="D8" t="n">
-        <v>5.542580412287738</v>
+        <v>7.241771902779489</v>
       </c>
       <c r="E8" t="n">
-        <v>11.53373538067712</v>
+        <v>17.49089000103038</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.988681014167726</v>
+        <v>1.598877461907258</v>
       </c>
       <c r="C9" t="n">
-        <v>5.274567557491197</v>
+        <v>10.31816945873498</v>
       </c>
       <c r="D9" t="n">
-        <v>5.994139998653631</v>
+        <v>7.644764289449125</v>
       </c>
       <c r="E9" t="n">
-        <v>13.25738857031256</v>
+        <v>19.56181121009136</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.491680807987767</v>
+        <v>1.006752818273977</v>
       </c>
       <c r="C10" t="n">
-        <v>6.231309901632598</v>
+        <v>7.619677726878939</v>
       </c>
       <c r="D10" t="n">
-        <v>6.547231486846128</v>
+        <v>5.995739396853163</v>
       </c>
       <c r="E10" t="n">
-        <v>15.27022219646649</v>
+        <v>14.62216994200608</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.022224760423847</v>
+        <v>0.9412015240614171</v>
       </c>
       <c r="C11" t="n">
-        <v>7.270699966978178</v>
+        <v>8.386412866418656</v>
       </c>
       <c r="D11" t="n">
-        <v>7.059305434685612</v>
+        <v>5.833868835376949</v>
       </c>
       <c r="E11" t="n">
-        <v>17.35223016208764</v>
+        <v>15.16148322585702</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.572090512977819</v>
+        <v>1.01428282316555</v>
       </c>
       <c r="C12" t="n">
-        <v>8.403893006093025</v>
+        <v>10.17832822864106</v>
       </c>
       <c r="D12" t="n">
-        <v>7.594404496077854</v>
+        <v>6.256442499715902</v>
       </c>
       <c r="E12" t="n">
-        <v>19.5703880151487</v>
+        <v>17.44905355152251</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.126070662719674</v>
+        <v>0.8030990745050184</v>
       </c>
       <c r="C13" t="n">
-        <v>9.568942623897643</v>
+        <v>9.888987545245442</v>
       </c>
       <c r="D13" t="n">
-        <v>8.150166537483443</v>
+        <v>5.70575075997274</v>
       </c>
       <c r="E13" t="n">
-        <v>21.84517982410076</v>
+        <v>16.3978373797232</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.371676651488317</v>
+        <v>0.8653909663394784</v>
       </c>
       <c r="C14" t="n">
-        <v>6.843498174424368</v>
+        <v>11.78800176452413</v>
       </c>
       <c r="D14" t="n">
-        <v>6.231584647844373</v>
+        <v>6.011309915442517</v>
       </c>
       <c r="E14" t="n">
-        <v>15.44675947375706</v>
+        <v>18.66470264630613</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.507530898801991</v>
+        <v>0.8341812068214723</v>
       </c>
       <c r="C15" t="n">
-        <v>7.208472700955163</v>
+        <v>12.90112694655325</v>
       </c>
       <c r="D15" t="n">
-        <v>6.284137602452706</v>
+        <v>6.025672884355648</v>
       </c>
       <c r="E15" t="n">
-        <v>16.00014120220986</v>
+        <v>19.76098103773037</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.996568882718455</v>
+        <v>0.9008026060316608</v>
       </c>
       <c r="C16" t="n">
-        <v>8.402376084089708</v>
+        <v>15.14766021818123</v>
       </c>
       <c r="D16" t="n">
-        <v>6.79279090550002</v>
+        <v>6.37301522211817</v>
       </c>
       <c r="E16" t="n">
-        <v>18.19173587230818</v>
+        <v>22.42147804633106</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.456588010428624</v>
+        <v>0.5342376482199869</v>
       </c>
       <c r="C17" t="n">
-        <v>7.702262343760181</v>
+        <v>11.38254978014724</v>
       </c>
       <c r="D17" t="n">
-        <v>6.341923272324673</v>
+        <v>5.268283982960361</v>
       </c>
       <c r="E17" t="n">
-        <v>16.50077362651348</v>
+        <v>17.18507141132759</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.875175779088336</v>
+        <v>0.4169187975624931</v>
       </c>
       <c r="C18" t="n">
-        <v>8.90114318775526</v>
+        <v>10.48329833548829</v>
       </c>
       <c r="D18" t="n">
-        <v>6.80750730358668</v>
+        <v>4.754388147172369</v>
       </c>
       <c r="E18" t="n">
-        <v>18.58382627043028</v>
+        <v>15.65460528022316</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.95800583289564</v>
+        <v>0.4804575089813465</v>
       </c>
       <c r="C19" t="n">
-        <v>9.476761501709248</v>
+        <v>13.00894247943364</v>
       </c>
       <c r="D19" t="n">
-        <v>6.968926261118942</v>
+        <v>5.235955031059514</v>
       </c>
       <c r="E19" t="n">
-        <v>19.40369359572383</v>
+        <v>18.7253550194745</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3.374934447935176</v>
+        <v>0.5387635051365646</v>
       </c>
       <c r="C20" t="n">
-        <v>10.8741910014112</v>
+        <v>15.61297917756309</v>
       </c>
       <c r="D20" t="n">
-        <v>7.436787947054801</v>
+        <v>5.637754913976607</v>
       </c>
       <c r="E20" t="n">
-        <v>21.68591339640118</v>
+        <v>21.78949759667626</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.04845585481914</v>
+        <v>0.5911790150663019</v>
       </c>
       <c r="C21" t="n">
-        <v>8.036655429303687</v>
+        <v>18.20195586590939</v>
       </c>
       <c r="D21" t="n">
-        <v>6.226067225746507</v>
+        <v>6.06187973968827</v>
       </c>
       <c r="E21" t="n">
-        <v>16.31117850986934</v>
+        <v>24.85501462066396</v>
       </c>
     </row>
   </sheetData>
